--- a/data/2026-10/reporte_2026-10-06.xlsx
+++ b/data/2026-10/reporte_2026-10-06.xlsx
@@ -7,7 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🛒 Comprar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚨 Flujo Completo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 Adjudicaciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📰 BORA Licitaciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🛒 Comprar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="⚠️ Riesgo Licitatorio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,6 +417,3135 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>en_comprar</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>procesos_comprar</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unidad_comprar</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>nro_proceso_comprar</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>cobro_en_tgn</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>beneficiario_tgn</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>monto_cobrado_tgn</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>metodo_cruce_tgn</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 54/2025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418643/20261006</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ARMANDO JOSE CUDINI – Autorización de venta INMOBILIARIA GABRIELA DI ORIO</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418644/20261006</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SEPULVEDA EDUARDO</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>20240385474</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>$161.000.795,88</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>❌ NO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>proveedor_adjudicado</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>texto_muestra</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 54/2025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2418643</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418643/20261006</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ARMANDO JOSE CUDINI – Autorización de venta INMOBILIARIA GABRIELA DI ORIO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL
+DE LA NACIÓN
+https://www.boletinoficial.gob.ar/pdf/linkQR/bWlsb3NqS2t5eTlSbkVWUVVZR3c4dz09
+Licitación Pública 54/2025
+EXPEDIENTE N°: EX-2025-58853-MPD-DGAD#MPD OBJETO: Adquisición de un inmueble; o inmueble
+con una superficie con predio libre </t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/25</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2418644</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418644/20261006</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SEPULVEDA EDUARDO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>20240385474</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>$161.000.795,88</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/pdf/linkQR/NDdzV016NU9tVUpSbkVWUVVZR3c4dz09
+AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO -
+DIRECCIÓN REGIONAL ADUANERA CUYO
+Licitación Pública 04/25
+PRORROGA  LICITACIÓN  PÚBLICA  04/25  DI  RACU  Expediente  Nº:  EX-2025-03067525-  -ARCA-
+SECFDVAFCU#SDGOAI Objeto d</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BORA Adjudicaciones</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha_extraccion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fecha_publicacion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organismo</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tipo_proceso</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>aviso_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>es_adjudicacion</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE DEFENSA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0050/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - COMBUSTIBLES, LUBRICANTES Y ACEITES</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2418587</t>
+        </is>
+      </c>
+      <c r="G2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418587/20261006</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>COMISIÓN NACIONAL DE ENERGÍA ATÓMICA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0007/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2418588</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418588/20261006</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE DEFENSA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0054/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2418589</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418589/20261006</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE DEFENSA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0056/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2418590</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418590/20261006</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>POLICÍA FEDERAL ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0068/2026</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2418591</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418591/20261006</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0375/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2418592</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418592/20261006</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0454/2026</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2418593</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418593/20261006</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0473/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2418594</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418594/20261006</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0670/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2418595</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418595/20261006</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0684/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2418596</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418596/20261006</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EJÉRCITO ARGENTINO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0687/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2418597</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418597/20261006</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HONORABLE SENADO DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Licitación Pública 11/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2418598</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418598/20261006</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ESTADO MAYOR CONJUNTO DE LAS FUERZAS ARMADAS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Licitación Pública 20/2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2418599</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418599/20261006</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HONORABLE CÁMARA DE DIPUTADOS DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Licitación Pública 21/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2418600</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418600/20261006</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Licitación Pública 222/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2418601</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418601/20261006</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COMISIÓN NACIONAL DE ENERGÍA ATÓMICA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Licitación Pública 3/2026</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2418602</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418602/20261006</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Licitación Pública 352/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2418603</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418603/20261006</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Concurso Privado BCYL0187-2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2418604</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418604/20261006</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Licitación Pública Nacional 49-2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EFECTOS VARIOS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2418605</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418605/20261006</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>POLICÍA FEDERAL ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0074/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQ. Y SUM. MEDICINA, ODONTOLOGIA Y VETERINARIA</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2418606</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418606/20261006</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Licitación Privada 104/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2418607</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418607/20261006</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE INFRAESTRUCTURAS FERROVIARIAS SOCIEDAD ANÓNIMA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Licitación Pública 11/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - EQUIPOS FERROVIARIOS, REPUESTOS Y SUMINISTROS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2418608</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418608/20261006</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0459/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2418609</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418609/20261006</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0460/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2418610</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418610/20261006</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0462/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2418611</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418611/20261006</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0463/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2418612</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418612/20261006</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0464/2026</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2418613</t>
+        </is>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418613/20261006</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0465/2026</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2418614</t>
+        </is>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418614/20261006</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0468/2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2418615</t>
+        </is>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418615/20261006</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0471/2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2418616</t>
+        </is>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418616/20261006</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0476/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2418617</t>
+        </is>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418617/20261006</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ARMADA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0477/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SUMINISTROS - PRODUCTOS ALIMENTICIOS</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2418618</t>
+        </is>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418618/20261006</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE LA PLATA - SECRETARÍA DE PLANEAMIENTO, OBRAS Y SERVICIOS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Licitación Pública 10/26</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2418619</t>
+        </is>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418619/20261006</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE LA PLATA - SECRETARÍA DE PLANEAMIENTO, OBRAS Y SERVICIOS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Licitación Pública 11/26</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2418620</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418620/20261006</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE ROSARIO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Licitación Pública 5/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2418621</t>
+        </is>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418621/20261006</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PODER JUDICIAL DE LA NACIÓN - CONSEJO DE LA MAGISTRATURA - ADMINISTRACIÓN GENERAL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Licitación Pública 601/26 (Obra Pública)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>OBRAS - CIVILES</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2418622</t>
+        </is>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418622/20261006</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL OESTE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Licitación Pública 19/26</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>SERVICIOS - LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2418623</t>
+        </is>
+      </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418623/20261006</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TEATRO NACIONAL CERVANTES</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0004/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2418624</t>
+        </is>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418624/20261006</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE LA PROPIEDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0006/2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2418625</t>
+        </is>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418625/20261006</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0013/2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2418626</t>
+        </is>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418626/20261006</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0014/2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2418627</t>
+        </is>
+      </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418627/20261006</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MINISTERIO DE SEGURIDAD NACIONAL</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Licitación Pública 0028/2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2418628</t>
+        </is>
+      </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418628/20261006</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Licitación Pública 02/2026 DOSC-DCU</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2418629</t>
+        </is>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418629/20261006</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CASA DE MONEDA SOCIEDAD ANÓNIMA UNIPERSONAL</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Licitación Pública 1004/2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2418630</t>
+        </is>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418630/20261006</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL NORTE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Licitación Pública 13/2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2418631</t>
+        </is>
+      </c>
+      <c r="G46" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418631/20261006</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SECRETARÍA DE CULTURA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Licitación Pública 3/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2418632</t>
+        </is>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418632/20261006</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>BANCO CENTRAL DE LA REPÚBLICA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Licitación Pública 40/26</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2418633</t>
+        </is>
+      </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418633/20261006</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>BANCO CENTRAL DE LA REPÚBLICA ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Licitación Pública 41/26</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2418634</t>
+        </is>
+      </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418634/20261006</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>PODER JUDICIAL DE LA NACIÓN - CONSEJO DE LA MAGISTRATURA - ADMINISTRACIÓN GENERAL</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Licitación Pública 637/2026</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2418635</t>
+        </is>
+      </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418635/20261006</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PODER JUDICIAL DE LA NACIÓN - CONSEJO DE LA MAGISTRATURA - ADMINISTRACIÓN GENERAL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Licitación Pública 638/2026</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2418636</t>
+        </is>
+      </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418636/20261006</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CASA DE MONEDA SOCIEDAD ANÓNIMA UNIPERSONAL</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Licitación Abreviada 755</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2418637</t>
+        </is>
+      </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418637/20261006</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>BANCO DE LA NACIÓN ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Licitación Pública CDB-3233</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2418638</t>
+        </is>
+      </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418638/20261006</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>BANCO DE LA NACIÓN ARGENTINA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Licitación Pública INM 6128</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2418639</t>
+        </is>
+      </c>
+      <c r="G54" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418639/20261006</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BELGRANO CARGAS Y LOGÍSTICA S.A.</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Licitación Pública Nacional 53-2026</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2418640</t>
+        </is>
+      </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418640/20261006</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE PARQUES NACIONALES Solicitud de Cotizaciones AR-APN-570369- CWRFQ</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SERVICIOS - SERVICIOS DIVERSOS</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2418641</t>
+        </is>
+      </c>
+      <c r="G56" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418641/20261006</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CENTRAL</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Licitación Pública 28/2026</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LOCACIONES - INMUEBLES (LOC)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2418642</t>
+        </is>
+      </c>
+      <c r="G57" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418642/20261006</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL MERCEDES</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>DICTAMEN DE EVALUACION - DICTAMEN DE EVALUACION</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2418645</t>
+        </is>
+      </c>
+      <c r="G58" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418645/20261006</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL PARANÁ</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Licitación Pública 08/2026</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>DICTAMEN DE EVALUACION - DICTAMEN DE EVALUACION</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2418646</t>
+        </is>
+      </c>
+      <c r="G59" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418646/20261006</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>BORA Sección 3ra</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1030,4 +4163,188 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organismo_contratante</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tipo_proceso_bora</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>cuit_proveedor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>monto_adjudicado_bora</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>indicadores_riesgo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>indice_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>nivel_riesgo_licit</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>etapa</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>link_bora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MINISTERIO PÚBLICO DE LA DEFENSA - DEFENSORÍA GENERAL DE LA NACIÓN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Licitación Pública 54/2025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>⚠️ SIN CUIT EXTRAÍDO</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418643/20261006</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AGENCIA DE RECAUDACIÓN Y CONTROL ADUANERO - DIRECCIÓN REGIONAL ADUANERA CUYO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Licitación Pública 04/25</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>20240385474</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>$161.000.795,88</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>✅ Sin alertas</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>✅ ADJUDICADO (sin pago aún)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>📋 SOLO BORA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.boletinoficial.gob.ar/detalleAviso/tercera/2418644/20261006</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>